--- a/v4/03_extracted/SituationChap_VALIDATION_TAUX_2025.xlsx
+++ b/v4/03_extracted/SituationChap_VALIDATION_TAUX_2025.xlsx
@@ -2011,7 +2011,7 @@
         <v>138</v>
       </c>
       <c r="L13">
-        <v>-1175000</v>
+        <v>0</v>
       </c>
       <c r="M13">
         <v>505500</v>
@@ -2020,7 +2020,7 @@
         <v>-1592670</v>
       </c>
       <c r="O13">
-        <v>923170</v>
+        <v>2098170</v>
       </c>
       <c r="P13">
         <v>500000</v>
@@ -2035,19 +2035,19 @@
         <v>236</v>
       </c>
       <c r="T13">
-        <v>-1175000</v>
+        <v>0</v>
       </c>
       <c r="U13">
         <v>139860</v>
       </c>
       <c r="V13">
-        <v>-1314860</v>
+        <v>-139860</v>
       </c>
       <c r="W13">
-        <v>940.1</v>
+        <v>100</v>
       </c>
       <c r="X13">
-        <v>-3769898.84</v>
+        <v>0</v>
       </c>
       <c r="Y13">
         <v>1419898.84</v>
@@ -2242,7 +2242,7 @@
         <v>141</v>
       </c>
       <c r="L16">
-        <v>-650000</v>
+        <v>0</v>
       </c>
       <c r="M16">
         <v>-62206</v>
@@ -2251,7 +2251,7 @@
         <v>-928088</v>
       </c>
       <c r="O16">
-        <v>215882</v>
+        <v>865882</v>
       </c>
       <c r="P16">
         <v>200000</v>
@@ -2266,19 +2266,19 @@
         <v>236</v>
       </c>
       <c r="T16">
-        <v>-586893.09</v>
+        <v>0</v>
       </c>
       <c r="U16">
         <v>408890.4</v>
       </c>
       <c r="V16">
-        <v>-995783.49</v>
+        <v>-408890.4</v>
       </c>
       <c r="W16">
-        <v>243.5</v>
+        <v>100</v>
       </c>
       <c r="X16">
-        <v>-2195496.95</v>
+        <v>0</v>
       </c>
       <c r="Y16">
         <v>1021710.76</v>
@@ -2506,7 +2506,7 @@
         <v>41.7</v>
       </c>
       <c r="X19">
-        <v>-1130251.07</v>
+        <v>0</v>
       </c>
       <c r="Y19">
         <v>1979871.93</v>
@@ -3003,7 +3003,7 @@
         <v>151</v>
       </c>
       <c r="L26">
-        <v>-9400000</v>
+        <v>0</v>
       </c>
       <c r="M26">
         <v>0</v>
@@ -3012,7 +3012,7 @@
         <v>-9630790</v>
       </c>
       <c r="O26">
-        <v>230790</v>
+        <v>9630790</v>
       </c>
       <c r="P26">
         <v>500000</v>
@@ -3027,19 +3027,19 @@
         <v>236</v>
       </c>
       <c r="T26">
-        <v>-9400000</v>
+        <v>0</v>
       </c>
       <c r="U26">
         <v>414450</v>
       </c>
       <c r="V26">
-        <v>-9814450</v>
+        <v>-414450</v>
       </c>
       <c r="W26">
-        <v>2368.1</v>
+        <v>100</v>
       </c>
       <c r="X26">
-        <v>-24079441.41</v>
+        <v>0</v>
       </c>
       <c r="Y26">
         <v>5279441.41</v>
@@ -4729,7 +4729,7 @@
         <v>174</v>
       </c>
       <c r="L49">
-        <v>-25000</v>
+        <v>0</v>
       </c>
       <c r="M49">
         <v>6596.5</v>
@@ -4738,7 +4738,7 @@
         <v>-5000</v>
       </c>
       <c r="O49">
-        <v>-13403.5</v>
+        <v>11596.5</v>
       </c>
       <c r="P49">
         <v>0</v>
@@ -4753,7 +4753,7 @@
         <v>236</v>
       </c>
       <c r="T49">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U49">
         <v>10000</v>
@@ -4765,7 +4765,7 @@
         <v>100</v>
       </c>
       <c r="X49">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y49">
         <v>0</v>
@@ -5807,7 +5807,7 @@
         <v>188</v>
       </c>
       <c r="L63">
-        <v>-1000000</v>
+        <v>0</v>
       </c>
       <c r="M63">
         <v>-65109.5</v>
@@ -5816,7 +5816,7 @@
         <v>685000</v>
       </c>
       <c r="O63">
-        <v>-1750109.5</v>
+        <v>-750109.5</v>
       </c>
       <c r="P63">
         <v>2000000</v>
@@ -5831,19 +5831,19 @@
         <v>236</v>
       </c>
       <c r="T63">
-        <v>-1000000</v>
+        <v>0</v>
       </c>
       <c r="U63">
         <v>6729370.7</v>
       </c>
       <c r="V63">
-        <v>-7729370.7</v>
+        <v>-6729370.7</v>
       </c>
       <c r="W63">
-        <v>114.9</v>
+        <v>100</v>
       </c>
       <c r="X63">
-        <v>-6709640.97</v>
+        <v>0</v>
       </c>
       <c r="Y63">
         <v>4709640.97</v>
@@ -8031,7 +8031,7 @@
         <v>217</v>
       </c>
       <c r="L92">
-        <v>-1863158</v>
+        <v>0</v>
       </c>
       <c r="M92">
         <v>305000</v>
@@ -8040,7 +8040,7 @@
         <v>-1397004</v>
       </c>
       <c r="O92">
-        <v>-161154</v>
+        <v>1702004</v>
       </c>
       <c r="P92">
         <v>0</v>
@@ -8055,19 +8055,19 @@
         <v>236</v>
       </c>
       <c r="T92">
-        <v>-1863158</v>
+        <v>0</v>
       </c>
       <c r="U92">
         <v>356757.02</v>
       </c>
       <c r="V92">
-        <v>-2219915.02</v>
+        <v>-356757.02</v>
       </c>
       <c r="W92">
-        <v>622.2</v>
+        <v>100</v>
       </c>
       <c r="X92">
-        <v>-4064017.98</v>
+        <v>0</v>
       </c>
       <c r="Y92">
         <v>337701.98</v>
@@ -8543,7 +8543,7 @@
         <v>30.4</v>
       </c>
       <c r="X99">
-        <v>-1520859.64</v>
+        <v>0</v>
       </c>
       <c r="Y99">
         <v>7320859.64</v>
@@ -8738,7 +8738,7 @@
         <v>227</v>
       </c>
       <c r="L102">
-        <v>-1466683.5</v>
+        <v>0</v>
       </c>
       <c r="M102">
         <v>-4751051</v>
@@ -8747,7 +8747,7 @@
         <v>-48178.5</v>
       </c>
       <c r="O102">
-        <v>-6169556</v>
+        <v>-4702872.5</v>
       </c>
       <c r="P102">
         <v>0</v>
@@ -8762,16 +8762,16 @@
         <v>236</v>
       </c>
       <c r="T102">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U102">
         <v>0</v>
       </c>
       <c r="V102">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="X102">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y102">
         <v>0</v>
@@ -8966,7 +8966,7 @@
         <v>230</v>
       </c>
       <c r="L105">
-        <v>-372500</v>
+        <v>0</v>
       </c>
       <c r="M105">
         <v>1012274</v>
@@ -8975,7 +8975,7 @@
         <v>-70864</v>
       </c>
       <c r="O105">
-        <v>710638</v>
+        <v>1083138</v>
       </c>
       <c r="P105">
         <v>0</v>
